--- a/Bao cao/TCB/TCB_Model_2026-07.xlsx
+++ b/Bao cao/TCB/TCB_Model_2026-07.xlsx
@@ -15207,7 +15207,7 @@
     <row r="4">
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Ngày lập: 01/07/2026 17:55</t>
+          <t>Ngày lập: 01/07/2026 18:20</t>
         </is>
       </c>
     </row>

--- a/Bao cao/TCB/TCB_Model_2026-07.xlsx
+++ b/Bao cao/TCB/TCB_Model_2026-07.xlsx
@@ -11303,75 +11303,75 @@
         </is>
       </c>
       <c r="B2" s="14">
-        <f>('04_PnL_Quarterly'!B2*4/'05_Balance_Sheet_Quarterly'!B4)*100</f>
+        <f>('04_PnL_Quarterly'!B2*4/(('05_Balance_Sheet_Quarterly'!B14+'05_Balance_Sheet_Quarterly'!B14)/2))*100</f>
         <v/>
       </c>
       <c r="C2" s="14">
-        <f>('04_PnL_Quarterly'!C2*4/'05_Balance_Sheet_Quarterly'!C4)*100</f>
+        <f>('04_PnL_Quarterly'!C2*4/(('05_Balance_Sheet_Quarterly'!B14+'05_Balance_Sheet_Quarterly'!C14)/2))*100</f>
         <v/>
       </c>
       <c r="D2" s="14">
-        <f>('04_PnL_Quarterly'!D2*4/'05_Balance_Sheet_Quarterly'!D4)*100</f>
+        <f>('04_PnL_Quarterly'!D2*4/(('05_Balance_Sheet_Quarterly'!C14+'05_Balance_Sheet_Quarterly'!D14)/2))*100</f>
         <v/>
       </c>
       <c r="E2" s="14">
-        <f>('04_PnL_Quarterly'!E2*4/'05_Balance_Sheet_Quarterly'!E4)*100</f>
+        <f>('04_PnL_Quarterly'!E2*4/(('05_Balance_Sheet_Quarterly'!D14+'05_Balance_Sheet_Quarterly'!E14)/2))*100</f>
         <v/>
       </c>
       <c r="F2" s="14">
-        <f>('04_PnL_Quarterly'!F2*4/'05_Balance_Sheet_Quarterly'!F4)*100</f>
+        <f>('04_PnL_Quarterly'!F2*4/(('05_Balance_Sheet_Quarterly'!E14+'05_Balance_Sheet_Quarterly'!F14)/2))*100</f>
         <v/>
       </c>
       <c r="G2" s="14">
-        <f>('04_PnL_Quarterly'!G2*4/'05_Balance_Sheet_Quarterly'!G4)*100</f>
+        <f>('04_PnL_Quarterly'!G2*4/(('05_Balance_Sheet_Quarterly'!F14+'05_Balance_Sheet_Quarterly'!G14)/2))*100</f>
         <v/>
       </c>
       <c r="H2" s="14">
-        <f>('04_PnL_Quarterly'!H2*4/'05_Balance_Sheet_Quarterly'!H4)*100</f>
+        <f>('04_PnL_Quarterly'!H2*4/(('05_Balance_Sheet_Quarterly'!G14+'05_Balance_Sheet_Quarterly'!H14)/2))*100</f>
         <v/>
       </c>
       <c r="I2" s="14">
-        <f>('04_PnL_Quarterly'!I2*4/'05_Balance_Sheet_Quarterly'!I4)*100</f>
+        <f>('04_PnL_Quarterly'!I2*4/(('05_Balance_Sheet_Quarterly'!H14+'05_Balance_Sheet_Quarterly'!I14)/2))*100</f>
         <v/>
       </c>
       <c r="J2" s="14">
-        <f>('04_PnL_Quarterly'!J2*4/'05_Balance_Sheet_Quarterly'!J4)*100</f>
+        <f>('04_PnL_Quarterly'!J2*4/(('05_Balance_Sheet_Quarterly'!I14+'05_Balance_Sheet_Quarterly'!J14)/2))*100</f>
         <v/>
       </c>
       <c r="K2" s="14">
-        <f>('04_PnL_Quarterly'!K2*4/'05_Balance_Sheet_Quarterly'!K4)*100</f>
+        <f>('04_PnL_Quarterly'!K2*4/(('05_Balance_Sheet_Quarterly'!J14+'05_Balance_Sheet_Quarterly'!K14)/2))*100</f>
         <v/>
       </c>
       <c r="L2" s="14">
-        <f>('04_PnL_Quarterly'!L2*4/'05_Balance_Sheet_Quarterly'!L4)*100</f>
+        <f>('04_PnL_Quarterly'!L2*4/(('05_Balance_Sheet_Quarterly'!K14+'05_Balance_Sheet_Quarterly'!L14)/2))*100</f>
         <v/>
       </c>
       <c r="M2" s="14">
-        <f>('04_PnL_Quarterly'!M2*4/'05_Balance_Sheet_Quarterly'!M4)*100</f>
+        <f>('04_PnL_Quarterly'!M2*4/(('05_Balance_Sheet_Quarterly'!L14+'05_Balance_Sheet_Quarterly'!M14)/2))*100</f>
         <v/>
       </c>
       <c r="N2" s="14">
-        <f>('04_PnL_Quarterly'!N2*4/'05_Balance_Sheet_Quarterly'!N4)*100</f>
+        <f>('04_PnL_Quarterly'!N2*4/(('05_Balance_Sheet_Quarterly'!M14+'05_Balance_Sheet_Quarterly'!N14)/2))*100</f>
         <v/>
       </c>
       <c r="O2" s="14">
-        <f>('04_PnL_Quarterly'!O2*4/'05_Balance_Sheet_Quarterly'!O4)*100</f>
+        <f>('04_PnL_Quarterly'!O2*4/(('05_Balance_Sheet_Quarterly'!N14+'05_Balance_Sheet_Quarterly'!O14)/2))*100</f>
         <v/>
       </c>
       <c r="P2" s="14">
-        <f>('04_PnL_Quarterly'!P2*4/'05_Balance_Sheet_Quarterly'!P4)*100</f>
+        <f>('04_PnL_Quarterly'!P2*4/(('05_Balance_Sheet_Quarterly'!O14+'05_Balance_Sheet_Quarterly'!P14)/2))*100</f>
         <v/>
       </c>
       <c r="Q2" s="14">
-        <f>('04_PnL_Quarterly'!Q2*4/'05_Balance_Sheet_Quarterly'!Q4)*100</f>
+        <f>('04_PnL_Quarterly'!Q2*4/(('05_Balance_Sheet_Quarterly'!P14+'05_Balance_Sheet_Quarterly'!Q14)/2))*100</f>
         <v/>
       </c>
       <c r="R2" s="14">
-        <f>('04_PnL_Quarterly'!R2*4/'05_Balance_Sheet_Quarterly'!R4)*100</f>
+        <f>('04_PnL_Quarterly'!R2*4/(('05_Balance_Sheet_Quarterly'!Q14+'05_Balance_Sheet_Quarterly'!R14)/2))*100</f>
         <v/>
       </c>
       <c r="S2" s="14">
-        <f>('04_PnL_Quarterly'!S2*4/'05_Balance_Sheet_Quarterly'!S4)*100</f>
+        <f>('04_PnL_Quarterly'!S2*4/(('05_Balance_Sheet_Quarterly'!R14+'05_Balance_Sheet_Quarterly'!S14)/2))*100</f>
         <v/>
       </c>
     </row>
@@ -11382,75 +11382,75 @@
         </is>
       </c>
       <c r="B3" s="14">
-        <f>('04_PnL_Quarterly'!B8*4/'05_Balance_Sheet_Quarterly'!B7)*100</f>
+        <f>('04_PnL_Quarterly'!B8*4/'05_Balance_Sheet_Quarterly'!B8)*100</f>
         <v/>
       </c>
       <c r="C3" s="14">
-        <f>('04_PnL_Quarterly'!C8*4/'05_Balance_Sheet_Quarterly'!C7)*100</f>
+        <f>('04_PnL_Quarterly'!C8*4/'05_Balance_Sheet_Quarterly'!C8)*100</f>
         <v/>
       </c>
       <c r="D3" s="14">
-        <f>('04_PnL_Quarterly'!D8*4/'05_Balance_Sheet_Quarterly'!D7)*100</f>
+        <f>('04_PnL_Quarterly'!D8*4/'05_Balance_Sheet_Quarterly'!D8)*100</f>
         <v/>
       </c>
       <c r="E3" s="14">
-        <f>('04_PnL_Quarterly'!E8*4/'05_Balance_Sheet_Quarterly'!E7)*100</f>
+        <f>('04_PnL_Quarterly'!E8*4/'05_Balance_Sheet_Quarterly'!E8)*100</f>
         <v/>
       </c>
       <c r="F3" s="14">
-        <f>('04_PnL_Quarterly'!F8*4/'05_Balance_Sheet_Quarterly'!F7)*100</f>
+        <f>('04_PnL_Quarterly'!F8*4/'05_Balance_Sheet_Quarterly'!F8)*100</f>
         <v/>
       </c>
       <c r="G3" s="14">
-        <f>('04_PnL_Quarterly'!G8*4/'05_Balance_Sheet_Quarterly'!G7)*100</f>
+        <f>('04_PnL_Quarterly'!G8*4/'05_Balance_Sheet_Quarterly'!G8)*100</f>
         <v/>
       </c>
       <c r="H3" s="14">
-        <f>('04_PnL_Quarterly'!H8*4/'05_Balance_Sheet_Quarterly'!H7)*100</f>
+        <f>('04_PnL_Quarterly'!H8*4/'05_Balance_Sheet_Quarterly'!H8)*100</f>
         <v/>
       </c>
       <c r="I3" s="14">
-        <f>('04_PnL_Quarterly'!I8*4/'05_Balance_Sheet_Quarterly'!I7)*100</f>
+        <f>('04_PnL_Quarterly'!I8*4/'05_Balance_Sheet_Quarterly'!I8)*100</f>
         <v/>
       </c>
       <c r="J3" s="14">
-        <f>('04_PnL_Quarterly'!J8*4/'05_Balance_Sheet_Quarterly'!J7)*100</f>
+        <f>('04_PnL_Quarterly'!J8*4/'05_Balance_Sheet_Quarterly'!J8)*100</f>
         <v/>
       </c>
       <c r="K3" s="14">
-        <f>('04_PnL_Quarterly'!K8*4/'05_Balance_Sheet_Quarterly'!K7)*100</f>
+        <f>('04_PnL_Quarterly'!K8*4/'05_Balance_Sheet_Quarterly'!K8)*100</f>
         <v/>
       </c>
       <c r="L3" s="14">
-        <f>('04_PnL_Quarterly'!L8*4/'05_Balance_Sheet_Quarterly'!L7)*100</f>
+        <f>('04_PnL_Quarterly'!L8*4/'05_Balance_Sheet_Quarterly'!L8)*100</f>
         <v/>
       </c>
       <c r="M3" s="14">
-        <f>('04_PnL_Quarterly'!M8*4/'05_Balance_Sheet_Quarterly'!M7)*100</f>
+        <f>('04_PnL_Quarterly'!M8*4/'05_Balance_Sheet_Quarterly'!M8)*100</f>
         <v/>
       </c>
       <c r="N3" s="14">
-        <f>('04_PnL_Quarterly'!N8*4/'05_Balance_Sheet_Quarterly'!N7)*100</f>
+        <f>('04_PnL_Quarterly'!N8*4/'05_Balance_Sheet_Quarterly'!N8)*100</f>
         <v/>
       </c>
       <c r="O3" s="14">
-        <f>('04_PnL_Quarterly'!O8*4/'05_Balance_Sheet_Quarterly'!O7)*100</f>
+        <f>('04_PnL_Quarterly'!O8*4/'05_Balance_Sheet_Quarterly'!O8)*100</f>
         <v/>
       </c>
       <c r="P3" s="14">
-        <f>('04_PnL_Quarterly'!P8*4/'05_Balance_Sheet_Quarterly'!P7)*100</f>
+        <f>('04_PnL_Quarterly'!P8*4/'05_Balance_Sheet_Quarterly'!P8)*100</f>
         <v/>
       </c>
       <c r="Q3" s="14">
-        <f>('04_PnL_Quarterly'!Q8*4/'05_Balance_Sheet_Quarterly'!Q7)*100</f>
+        <f>('04_PnL_Quarterly'!Q8*4/'05_Balance_Sheet_Quarterly'!Q8)*100</f>
         <v/>
       </c>
       <c r="R3" s="14">
-        <f>('04_PnL_Quarterly'!R8*4/'05_Balance_Sheet_Quarterly'!R7)*100</f>
+        <f>('04_PnL_Quarterly'!R8*4/'05_Balance_Sheet_Quarterly'!R8)*100</f>
         <v/>
       </c>
       <c r="S3" s="14">
-        <f>('04_PnL_Quarterly'!S8*4/'05_Balance_Sheet_Quarterly'!S7)*100</f>
+        <f>('04_PnL_Quarterly'!S8*4/'05_Balance_Sheet_Quarterly'!S8)*100</f>
         <v/>
       </c>
     </row>
@@ -11461,75 +11461,75 @@
         </is>
       </c>
       <c r="B4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!B4/'05_Balance_Sheet_Quarterly'!B6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!B5/('05_Balance_Sheet_Quarterly'!B7+'05_Balance_Sheet_Quarterly'!B10))*100</f>
         <v/>
       </c>
       <c r="C4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!C4/'05_Balance_Sheet_Quarterly'!C6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!C5/('05_Balance_Sheet_Quarterly'!C7+'05_Balance_Sheet_Quarterly'!C10))*100</f>
         <v/>
       </c>
       <c r="D4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!D4/'05_Balance_Sheet_Quarterly'!D6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!D5/('05_Balance_Sheet_Quarterly'!D7+'05_Balance_Sheet_Quarterly'!D10))*100</f>
         <v/>
       </c>
       <c r="E4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!E4/'05_Balance_Sheet_Quarterly'!E6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!E5/('05_Balance_Sheet_Quarterly'!E7+'05_Balance_Sheet_Quarterly'!E10))*100</f>
         <v/>
       </c>
       <c r="F4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!F4/'05_Balance_Sheet_Quarterly'!F6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!F5/('05_Balance_Sheet_Quarterly'!F7+'05_Balance_Sheet_Quarterly'!F10))*100</f>
         <v/>
       </c>
       <c r="G4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!G4/'05_Balance_Sheet_Quarterly'!G6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!G5/('05_Balance_Sheet_Quarterly'!G7+'05_Balance_Sheet_Quarterly'!G10))*100</f>
         <v/>
       </c>
       <c r="H4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!H4/'05_Balance_Sheet_Quarterly'!H6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!H5/('05_Balance_Sheet_Quarterly'!H7+'05_Balance_Sheet_Quarterly'!H10))*100</f>
         <v/>
       </c>
       <c r="I4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!I4/'05_Balance_Sheet_Quarterly'!I6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!I5/('05_Balance_Sheet_Quarterly'!I7+'05_Balance_Sheet_Quarterly'!I10))*100</f>
         <v/>
       </c>
       <c r="J4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!J4/'05_Balance_Sheet_Quarterly'!J6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!J5/('05_Balance_Sheet_Quarterly'!J7+'05_Balance_Sheet_Quarterly'!J10))*100</f>
         <v/>
       </c>
       <c r="K4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!K4/'05_Balance_Sheet_Quarterly'!K6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!K5/('05_Balance_Sheet_Quarterly'!K7+'05_Balance_Sheet_Quarterly'!K10))*100</f>
         <v/>
       </c>
       <c r="L4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!L4/'05_Balance_Sheet_Quarterly'!L6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!L5/('05_Balance_Sheet_Quarterly'!L7+'05_Balance_Sheet_Quarterly'!L10))*100</f>
         <v/>
       </c>
       <c r="M4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!M4/'05_Balance_Sheet_Quarterly'!M6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!M5/('05_Balance_Sheet_Quarterly'!M7+'05_Balance_Sheet_Quarterly'!M10))*100</f>
         <v/>
       </c>
       <c r="N4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!N4/'05_Balance_Sheet_Quarterly'!N6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!N5/('05_Balance_Sheet_Quarterly'!N7+'05_Balance_Sheet_Quarterly'!N10))*100</f>
         <v/>
       </c>
       <c r="O4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!O4/'05_Balance_Sheet_Quarterly'!O6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!O5/('05_Balance_Sheet_Quarterly'!O7+'05_Balance_Sheet_Quarterly'!O10))*100</f>
         <v/>
       </c>
       <c r="P4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!P4/'05_Balance_Sheet_Quarterly'!P6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!P5/('05_Balance_Sheet_Quarterly'!P7+'05_Balance_Sheet_Quarterly'!P10))*100</f>
         <v/>
       </c>
       <c r="Q4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!Q4/'05_Balance_Sheet_Quarterly'!Q6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!Q5/('05_Balance_Sheet_Quarterly'!Q7+'05_Balance_Sheet_Quarterly'!Q10))*100</f>
         <v/>
       </c>
       <c r="R4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!R4/'05_Balance_Sheet_Quarterly'!R6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!R5/('05_Balance_Sheet_Quarterly'!R7+'05_Balance_Sheet_Quarterly'!R10))*100</f>
         <v/>
       </c>
       <c r="S4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!S4/'05_Balance_Sheet_Quarterly'!S6)*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!S5/('05_Balance_Sheet_Quarterly'!S7+'05_Balance_Sheet_Quarterly'!S10))*100</f>
         <v/>
       </c>
     </row>
@@ -11540,75 +11540,75 @@
         </is>
       </c>
       <c r="B5" s="14">
-        <f>('04_PnL_Quarterly'!B10*4/'05_Balance_Sheet_Quarterly'!B6)*100</f>
+        <f>('04_PnL_Quarterly'!B10*4/'05_Balance_Sheet_Quarterly'!B7)*100</f>
         <v/>
       </c>
       <c r="C5" s="14">
-        <f>('04_PnL_Quarterly'!C10*4/'05_Balance_Sheet_Quarterly'!C6)*100</f>
+        <f>('04_PnL_Quarterly'!C10*4/'05_Balance_Sheet_Quarterly'!C7)*100</f>
         <v/>
       </c>
       <c r="D5" s="14">
-        <f>('04_PnL_Quarterly'!D10*4/'05_Balance_Sheet_Quarterly'!D6)*100</f>
+        <f>('04_PnL_Quarterly'!D10*4/'05_Balance_Sheet_Quarterly'!D7)*100</f>
         <v/>
       </c>
       <c r="E5" s="14">
-        <f>('04_PnL_Quarterly'!E10*4/'05_Balance_Sheet_Quarterly'!E6)*100</f>
+        <f>('04_PnL_Quarterly'!E10*4/'05_Balance_Sheet_Quarterly'!E7)*100</f>
         <v/>
       </c>
       <c r="F5" s="14">
-        <f>('04_PnL_Quarterly'!F10*4/'05_Balance_Sheet_Quarterly'!F6)*100</f>
+        <f>('04_PnL_Quarterly'!F10*4/'05_Balance_Sheet_Quarterly'!F7)*100</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>('04_PnL_Quarterly'!G10*4/'05_Balance_Sheet_Quarterly'!G6)*100</f>
+        <f>('04_PnL_Quarterly'!G10*4/'05_Balance_Sheet_Quarterly'!G7)*100</f>
         <v/>
       </c>
       <c r="H5" s="14">
-        <f>('04_PnL_Quarterly'!H10*4/'05_Balance_Sheet_Quarterly'!H6)*100</f>
+        <f>('04_PnL_Quarterly'!H10*4/'05_Balance_Sheet_Quarterly'!H7)*100</f>
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>('04_PnL_Quarterly'!I10*4/'05_Balance_Sheet_Quarterly'!I6)*100</f>
+        <f>('04_PnL_Quarterly'!I10*4/'05_Balance_Sheet_Quarterly'!I7)*100</f>
         <v/>
       </c>
       <c r="J5" s="14">
-        <f>('04_PnL_Quarterly'!J10*4/'05_Balance_Sheet_Quarterly'!J6)*100</f>
+        <f>('04_PnL_Quarterly'!J10*4/'05_Balance_Sheet_Quarterly'!J7)*100</f>
         <v/>
       </c>
       <c r="K5" s="14">
-        <f>('04_PnL_Quarterly'!K10*4/'05_Balance_Sheet_Quarterly'!K6)*100</f>
+        <f>('04_PnL_Quarterly'!K10*4/'05_Balance_Sheet_Quarterly'!K7)*100</f>
         <v/>
       </c>
       <c r="L5" s="14">
-        <f>('04_PnL_Quarterly'!L10*4/'05_Balance_Sheet_Quarterly'!L6)*100</f>
+        <f>('04_PnL_Quarterly'!L10*4/'05_Balance_Sheet_Quarterly'!L7)*100</f>
         <v/>
       </c>
       <c r="M5" s="14">
-        <f>('04_PnL_Quarterly'!M10*4/'05_Balance_Sheet_Quarterly'!M6)*100</f>
+        <f>('04_PnL_Quarterly'!M10*4/'05_Balance_Sheet_Quarterly'!M7)*100</f>
         <v/>
       </c>
       <c r="N5" s="14">
-        <f>('04_PnL_Quarterly'!N10*4/'05_Balance_Sheet_Quarterly'!N6)*100</f>
+        <f>('04_PnL_Quarterly'!N10*4/'05_Balance_Sheet_Quarterly'!N7)*100</f>
         <v/>
       </c>
       <c r="O5" s="14">
-        <f>('04_PnL_Quarterly'!O10*4/'05_Balance_Sheet_Quarterly'!O6)*100</f>
+        <f>('04_PnL_Quarterly'!O10*4/'05_Balance_Sheet_Quarterly'!O7)*100</f>
         <v/>
       </c>
       <c r="P5" s="14">
-        <f>('04_PnL_Quarterly'!P10*4/'05_Balance_Sheet_Quarterly'!P6)*100</f>
+        <f>('04_PnL_Quarterly'!P10*4/'05_Balance_Sheet_Quarterly'!P7)*100</f>
         <v/>
       </c>
       <c r="Q5" s="14">
-        <f>('04_PnL_Quarterly'!Q10*4/'05_Balance_Sheet_Quarterly'!Q6)*100</f>
+        <f>('04_PnL_Quarterly'!Q10*4/'05_Balance_Sheet_Quarterly'!Q7)*100</f>
         <v/>
       </c>
       <c r="R5" s="14">
-        <f>('04_PnL_Quarterly'!R10*4/'05_Balance_Sheet_Quarterly'!R6)*100</f>
+        <f>('04_PnL_Quarterly'!R10*4/'05_Balance_Sheet_Quarterly'!R7)*100</f>
         <v/>
       </c>
       <c r="S5" s="14">
-        <f>('04_PnL_Quarterly'!S10*4/'05_Balance_Sheet_Quarterly'!S6)*100</f>
+        <f>('04_PnL_Quarterly'!S10*4/'05_Balance_Sheet_Quarterly'!S7)*100</f>
         <v/>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="B13" s="21">
-        <f>PERCENTILE('13_PE_PB_History'!C2:C32, 0.25)</f>
+        <f t="array" ref="B13">MEDIAN(SMALL('13_PE_PB_History'!C2:C32, ROW(INDIRECT("1:"&amp;CEILING(COUNT('13_PE_PB_History'!C2:C32)/2,1)))))</f>
         <v/>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -12157,11 +12157,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P/B chốt lời (x) — BÁN / CHỐT LỜI</t>
+          <t>P/B Over (x) — BÁN / CHỐT LỜI</t>
         </is>
       </c>
       <c r="B15" s="24">
-        <f>PERCENTILE('13_PE_PB_History'!C2:C32, 0.75)</f>
+        <f t="array" ref="B15">MEDIAN(LARGE('13_PE_PB_History'!C2:C32, ROW(INDIRECT("1:"&amp;CEILING(COUNT('13_PE_PB_History'!C2:C32)/2,1)))))</f>
         <v/>
       </c>
       <c r="C15" s="25" t="inlineStr">
@@ -12408,19 +12408,19 @@
         <v>0.08</v>
       </c>
       <c r="B3" s="19" t="n">
-        <v>34173.52605783359</v>
+        <v>43507.68476106286</v>
       </c>
       <c r="C3" s="19" t="n">
-        <v>35465.38881499652</v>
+        <v>46278.01793164518</v>
       </c>
       <c r="D3" s="19" t="n">
-        <v>37273.99667502464</v>
+        <v>50156.48437046042</v>
       </c>
       <c r="E3" s="19" t="n">
-        <v>39986.90846506681</v>
+        <v>55974.18402868329</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>44508.4281151371</v>
+        <v>65670.35012572139</v>
       </c>
     </row>
     <row r="4">
@@ -12428,19 +12428,19 @@
         <v>0.1</v>
       </c>
       <c r="B4" s="19" t="n">
-        <v>32203.81099855963</v>
+        <v>39303.44871572265</v>
       </c>
       <c r="C4" s="19" t="n">
-        <v>32930.24357705026</v>
+        <v>40861.24597957738</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>33864.22832082392</v>
+        <v>42864.12817596201</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>35109.54131252215</v>
+        <v>45534.63777114153</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>36852.97950089967</v>
+        <v>49273.35120439285</v>
       </c>
     </row>
     <row r="5">
@@ -12448,19 +12448,19 @@
         <v>0.12</v>
       </c>
       <c r="B5" s="19" t="n">
-        <v>30950.31109026766</v>
+        <v>36634.20450927032</v>
       </c>
       <c r="C5" s="29" t="n">
-        <v>31408.96431265652</v>
+        <v>37617.7627307092</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>31969.54047335401</v>
+        <v>38819.88944580117</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>32670.26067422587</v>
+        <v>40322.54783966613</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>33571.18664677541</v>
+        <v>42254.5372032068</v>
       </c>
     </row>
     <row r="6">
@@ -12468,19 +12468,19 @@
         <v>0.14</v>
       </c>
       <c r="B6" s="19" t="n">
-        <v>30082.47547180044</v>
+        <v>34791.15977813784</v>
       </c>
       <c r="C6" s="29" t="n">
-        <v>30394.63664090822</v>
+        <v>35460.57333352679</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>30763.5543862174</v>
+        <v>36251.698444441</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>31206.25568058842</v>
+        <v>37201.04857753806</v>
       </c>
       <c r="F6" s="19" t="n">
-        <v>31747.33504037523</v>
+        <v>38361.3654068789</v>
       </c>
     </row>
     <row r="7">
@@ -12488,19 +12488,19 @@
         <v>0.16</v>
       </c>
       <c r="B7" s="19" t="n">
-        <v>29446.04600953521</v>
+        <v>33443.56824188426</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>29670.00985019437</v>
+        <v>33923.84716729556</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>29928.42966633956</v>
+        <v>34478.01515815475</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>30229.91945184228</v>
+        <v>35124.54448082381</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>30586.22556198186</v>
+        <v>35888.62458943269</v>
       </c>
     </row>
   </sheetData>
@@ -15207,7 +15207,7 @@
     <row r="4">
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Ngày lập: 01/07/2026 20:53</t>
+          <t>Ngày lập: 01/07/2026 22:50</t>
         </is>
       </c>
     </row>
@@ -15387,17 +15387,14 @@
         <f>(SUM('05_Balance_Sheet'!F3:F4)-SUM('05_Balance_Sheet'!E3:E4))/SUM('05_Balance_Sheet'!E3:E4)</f>
         <v/>
       </c>
-      <c r="G4" s="4">
-        <f>MEDIAN(C4:F4)*0.9</f>
-        <v/>
-      </c>
-      <c r="H4" s="4">
-        <f>MAX(G4-0.01,0.05)</f>
-        <v/>
-      </c>
-      <c r="I4" s="4">
-        <f>MAX(H4-0.01,0.05)</f>
-        <v/>
+      <c r="G4" s="4" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0.171</v>
       </c>
     </row>
     <row r="5">
@@ -15703,7 +15700,7 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>P/B mục tiêu (x)</t>
+          <t>P/B Over (x)</t>
         </is>
       </c>
       <c r="B15" s="14" t="n"/>
@@ -16116,13 +16113,13 @@
         <v>0.0378</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>0.0374</v>
+        <v>0.038</v>
       </c>
       <c r="H4" s="17" t="n">
-        <v>0.0373</v>
+        <v>0.0391</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.037</v>
+        <v>0.0399</v>
       </c>
     </row>
     <row r="5">
@@ -17446,7 +17443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17614,58 +17611,58 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>3578.643</v>
+        <v>8487.172</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>3276.768</v>
+        <v>12275.92</v>
       </c>
       <c r="D3" s="17" t="n">
-        <v>3204.43</v>
+        <v>8018.252</v>
       </c>
       <c r="E3" s="17" t="n">
-        <v>3025.551</v>
+        <v>7734.356</v>
       </c>
       <c r="F3" s="17" t="n">
-        <v>4215.721</v>
+        <v>15691.311</v>
       </c>
       <c r="G3" s="17" t="n">
-        <v>2852.199</v>
+        <v>18686.633</v>
       </c>
       <c r="H3" s="17" t="n">
-        <v>3112.603</v>
+        <v>10972.959</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>3505.804</v>
+        <v>30934.346</v>
       </c>
       <c r="J3" s="17" t="n">
-        <v>3620.695</v>
+        <v>30761.287</v>
       </c>
       <c r="K3" s="17" t="n">
-        <v>3665.067</v>
+        <v>17252.786</v>
       </c>
       <c r="L3" s="17" t="n">
-        <v>3638.265</v>
+        <v>31693.359</v>
       </c>
       <c r="M3" s="17" t="n">
-        <v>3608.503</v>
+        <v>44223.252</v>
       </c>
       <c r="N3" s="17" t="n">
-        <v>3384.77</v>
+        <v>57737.923</v>
       </c>
       <c r="O3" s="17" t="n">
-        <v>3789.947</v>
+        <v>66488.939</v>
       </c>
       <c r="P3" s="17" t="n">
-        <v>3666.435</v>
+        <v>52152.092</v>
       </c>
       <c r="Q3" s="17" t="n">
-        <v>4045.689</v>
+        <v>81632.149</v>
       </c>
       <c r="R3" s="17" t="n">
-        <v>4360.821</v>
+        <v>86523.59299999999</v>
       </c>
       <c r="S3" s="17" t="n">
-        <v>5467.7</v>
+        <v>98475.058</v>
       </c>
     </row>
     <row r="4">
@@ -18276,6 +18273,67 @@
       </c>
       <c r="S13" s="17" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Tài sản sinh lãi (IEA)</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>520262.995</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>566922.8910000001</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>565151.802</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>589405.213</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>617969.241</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>644742.059</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>650766.91</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>691152.086</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>752341.2240000002</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>790093.2890000001</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>818987.808</v>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>854297.351</v>
+      </c>
+      <c r="N14" s="17" t="n">
+        <v>914586.304</v>
+      </c>
+      <c r="O14" s="17" t="n">
+        <v>927758.233</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>980785.308</v>
+      </c>
+      <c r="Q14" s="17" t="n">
+        <v>1070005.703</v>
+      </c>
+      <c r="R14" s="17" t="n">
+        <v>1104127.06</v>
+      </c>
+      <c r="S14" s="17" t="n">
+        <v>1112928.9</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/TCB/TCB_Model_2026-07.xlsx
+++ b/Bao cao/TCB/TCB_Model_2026-07.xlsx
@@ -11461,75 +11461,75 @@
         </is>
       </c>
       <c r="B4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!B5/('05_Balance_Sheet_Quarterly'!B7+'05_Balance_Sheet_Quarterly'!B10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!B15/'05_Balance_Sheet_Quarterly'!B16)*100</f>
         <v/>
       </c>
       <c r="C4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!C5/('05_Balance_Sheet_Quarterly'!C7+'05_Balance_Sheet_Quarterly'!C10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!C15/'05_Balance_Sheet_Quarterly'!C16)*100</f>
         <v/>
       </c>
       <c r="D4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!D5/('05_Balance_Sheet_Quarterly'!D7+'05_Balance_Sheet_Quarterly'!D10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!D15/'05_Balance_Sheet_Quarterly'!D16)*100</f>
         <v/>
       </c>
       <c r="E4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!E5/('05_Balance_Sheet_Quarterly'!E7+'05_Balance_Sheet_Quarterly'!E10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!E15/'05_Balance_Sheet_Quarterly'!E16)*100</f>
         <v/>
       </c>
       <c r="F4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!F5/('05_Balance_Sheet_Quarterly'!F7+'05_Balance_Sheet_Quarterly'!F10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!F15/'05_Balance_Sheet_Quarterly'!F16)*100</f>
         <v/>
       </c>
       <c r="G4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!G5/('05_Balance_Sheet_Quarterly'!G7+'05_Balance_Sheet_Quarterly'!G10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!G15/'05_Balance_Sheet_Quarterly'!G16)*100</f>
         <v/>
       </c>
       <c r="H4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!H5/('05_Balance_Sheet_Quarterly'!H7+'05_Balance_Sheet_Quarterly'!H10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!H15/'05_Balance_Sheet_Quarterly'!H16)*100</f>
         <v/>
       </c>
       <c r="I4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!I5/('05_Balance_Sheet_Quarterly'!I7+'05_Balance_Sheet_Quarterly'!I10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!I15/'05_Balance_Sheet_Quarterly'!I16)*100</f>
         <v/>
       </c>
       <c r="J4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!J5/('05_Balance_Sheet_Quarterly'!J7+'05_Balance_Sheet_Quarterly'!J10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!J15/'05_Balance_Sheet_Quarterly'!J16)*100</f>
         <v/>
       </c>
       <c r="K4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!K5/('05_Balance_Sheet_Quarterly'!K7+'05_Balance_Sheet_Quarterly'!K10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!K15/'05_Balance_Sheet_Quarterly'!K16)*100</f>
         <v/>
       </c>
       <c r="L4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!L5/('05_Balance_Sheet_Quarterly'!L7+'05_Balance_Sheet_Quarterly'!L10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!L15/'05_Balance_Sheet_Quarterly'!L16)*100</f>
         <v/>
       </c>
       <c r="M4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!M5/('05_Balance_Sheet_Quarterly'!M7+'05_Balance_Sheet_Quarterly'!M10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!M15/'05_Balance_Sheet_Quarterly'!M16)*100</f>
         <v/>
       </c>
       <c r="N4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!N5/('05_Balance_Sheet_Quarterly'!N7+'05_Balance_Sheet_Quarterly'!N10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!N15/'05_Balance_Sheet_Quarterly'!N16)*100</f>
         <v/>
       </c>
       <c r="O4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!O5/('05_Balance_Sheet_Quarterly'!O7+'05_Balance_Sheet_Quarterly'!O10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!O15/'05_Balance_Sheet_Quarterly'!O16)*100</f>
         <v/>
       </c>
       <c r="P4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!P5/('05_Balance_Sheet_Quarterly'!P7+'05_Balance_Sheet_Quarterly'!P10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!P15/'05_Balance_Sheet_Quarterly'!P16)*100</f>
         <v/>
       </c>
       <c r="Q4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!Q5/('05_Balance_Sheet_Quarterly'!Q7+'05_Balance_Sheet_Quarterly'!Q10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!Q15/'05_Balance_Sheet_Quarterly'!Q16)*100</f>
         <v/>
       </c>
       <c r="R4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!R5/('05_Balance_Sheet_Quarterly'!R7+'05_Balance_Sheet_Quarterly'!R10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!R15/'05_Balance_Sheet_Quarterly'!R16)*100</f>
         <v/>
       </c>
       <c r="S4" s="14">
-        <f>('05_Balance_Sheet_Quarterly'!S5/('05_Balance_Sheet_Quarterly'!S7+'05_Balance_Sheet_Quarterly'!S10))*100</f>
+        <f>('05_Balance_Sheet_Quarterly'!S15/'05_Balance_Sheet_Quarterly'!S16)*100</f>
         <v/>
       </c>
     </row>
@@ -11820,36 +11820,36 @@
           <t>LDR — điều chỉnh (%)</t>
         </is>
       </c>
-      <c r="B6" s="16">
-        <f>SUM('05_Balance_Sheet'!B3:B4)/(SUM('05_Balance_Sheet'!B5:B6)+'05_Balance_Sheet'!B7*0.0-'05_Balance_Sheet'!B8-'05_Balance_Sheet'!B9)</f>
-        <v/>
-      </c>
-      <c r="C6" s="16">
-        <f>SUM('05_Balance_Sheet'!C3:C4)/(SUM('05_Balance_Sheet'!C5:C6)+'05_Balance_Sheet'!C7*0.0-'05_Balance_Sheet'!C8-'05_Balance_Sheet'!C9)</f>
-        <v/>
-      </c>
-      <c r="D6" s="16">
-        <f>SUM('05_Balance_Sheet'!D3:D4)/(SUM('05_Balance_Sheet'!D5:D6)+'05_Balance_Sheet'!D7*0.35-'05_Balance_Sheet'!D8-'05_Balance_Sheet'!D9)</f>
-        <v/>
-      </c>
-      <c r="E6" s="16">
-        <f>SUM('05_Balance_Sheet'!E3:E4)/(SUM('05_Balance_Sheet'!E5:E6)+'05_Balance_Sheet'!E7*0.5-'05_Balance_Sheet'!E8-'05_Balance_Sheet'!E9)</f>
-        <v/>
-      </c>
-      <c r="F6" s="16">
-        <f>SUM('05_Balance_Sheet'!F3:F4)/(SUM('05_Balance_Sheet'!F5:F6)+'05_Balance_Sheet'!F7*0.6-'05_Balance_Sheet'!F8-'05_Balance_Sheet'!F9)</f>
-        <v/>
-      </c>
-      <c r="G6" s="16">
-        <f>SUM('05_Balance_Sheet'!G3:G4)/(SUM('05_Balance_Sheet'!G5:G6)+'05_Balance_Sheet'!G7*0.2-'05_Balance_Sheet'!G8-'05_Balance_Sheet'!G9)</f>
-        <v/>
-      </c>
-      <c r="H6" s="16">
-        <f>SUM('05_Balance_Sheet'!H3:H4)/(SUM('05_Balance_Sheet'!H5:H6)+'05_Balance_Sheet'!H7*0.2-'05_Balance_Sheet'!H8-'05_Balance_Sheet'!H9)</f>
+      <c r="B6" s="14">
+        <f>'05_Balance_Sheet'!B11/'05_Balance_Sheet'!B12</f>
+        <v/>
+      </c>
+      <c r="C6" s="14">
+        <f>'05_Balance_Sheet'!C11/'05_Balance_Sheet'!C12</f>
+        <v/>
+      </c>
+      <c r="D6" s="14">
+        <f>'05_Balance_Sheet'!D11/'05_Balance_Sheet'!D12</f>
+        <v/>
+      </c>
+      <c r="E6" s="14">
+        <f>'05_Balance_Sheet'!E11/'05_Balance_Sheet'!E12</f>
+        <v/>
+      </c>
+      <c r="F6" s="14">
+        <f>'05_Balance_Sheet'!F11/'05_Balance_Sheet'!F12</f>
+        <v/>
+      </c>
+      <c r="G6" s="14">
+        <f>'05_Balance_Sheet'!G11/'05_Balance_Sheet'!G12</f>
+        <v/>
+      </c>
+      <c r="H6" s="14">
+        <f>'05_Balance_Sheet'!H11/'05_Balance_Sheet'!H12</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>SUM('05_Balance_Sheet'!I3:I4)/(SUM('05_Balance_Sheet'!I5:I6)+'05_Balance_Sheet'!I7*0.2-'05_Balance_Sheet'!I8-'05_Balance_Sheet'!I9)</f>
+        <f>'05_Balance_Sheet'!I11/'05_Balance_Sheet'!I12</f>
         <v/>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
     <row r="4">
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Ngày lập: 01/07/2026 22:50</t>
+          <t>Ngày lập: 02/07/2026 00:01</t>
         </is>
       </c>
     </row>
@@ -15387,14 +15387,17 @@
         <f>(SUM('05_Balance_Sheet'!F3:F4)-SUM('05_Balance_Sheet'!E3:E4))/SUM('05_Balance_Sheet'!E3:E4)</f>
         <v/>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0.171</v>
+      <c r="G4" s="4">
+        <f>AVERAGE(D4:F4)*0.9</f>
+        <v/>
+      </c>
+      <c r="H4" s="4">
+        <f>MAX(G4-0.01,0.05)</f>
+        <v/>
+      </c>
+      <c r="I4" s="4">
+        <f>MAX(H4-0.01,0.05)</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -17443,7 +17446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18334,6 +18337,225 @@
       </c>
       <c r="S14" s="17" t="n">
         <v>1112928.9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Tổng tín dụng (tỷ)</t>
+        </is>
+      </c>
+      <c r="B15" s="17">
+        <f>B5+B9</f>
+        <v/>
+      </c>
+      <c r="C15" s="17">
+        <f>C5+C9</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>D5+D9</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>E5+E9</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>F5+F9</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>G5+G9</f>
+        <v/>
+      </c>
+      <c r="H15" s="17">
+        <f>H5+H9</f>
+        <v/>
+      </c>
+      <c r="I15" s="17">
+        <f>I5+I9</f>
+        <v/>
+      </c>
+      <c r="J15" s="17">
+        <f>J5+J9</f>
+        <v/>
+      </c>
+      <c r="K15" s="17">
+        <f>K5+K9</f>
+        <v/>
+      </c>
+      <c r="L15" s="17">
+        <f>L5+L9</f>
+        <v/>
+      </c>
+      <c r="M15" s="17">
+        <f>M5+M9</f>
+        <v/>
+      </c>
+      <c r="N15" s="17">
+        <f>N5+N9</f>
+        <v/>
+      </c>
+      <c r="O15" s="17">
+        <f>O5+O9</f>
+        <v/>
+      </c>
+      <c r="P15" s="17">
+        <f>P5+P9</f>
+        <v/>
+      </c>
+      <c r="Q15" s="17">
+        <f>Q5+Q9</f>
+        <v/>
+      </c>
+      <c r="R15" s="17">
+        <f>R5+R9</f>
+        <v/>
+      </c>
+      <c r="S15" s="17">
+        <f>S5+S9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Tổng huy động (tỷ)</t>
+        </is>
+      </c>
+      <c r="B16" s="17">
+        <f>B7+B10+B17+B11*0.0-B12-B13</f>
+        <v/>
+      </c>
+      <c r="C16" s="17">
+        <f>C7+C10+C17+C11*0.0-C12-C13</f>
+        <v/>
+      </c>
+      <c r="D16" s="17">
+        <f>D7+D10+D17+D11*0.0-D12-D13</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>E7+E10+E17+E11*0.0-E12-E13</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>F7+F10+F17+F11*0.0-F12-F13</f>
+        <v/>
+      </c>
+      <c r="G16" s="17">
+        <f>G7+G10+G17+G11*0.5-G12-G13</f>
+        <v/>
+      </c>
+      <c r="H16" s="17">
+        <f>H7+H10+H17+H11*0.5-H12-H13</f>
+        <v/>
+      </c>
+      <c r="I16" s="17">
+        <f>I7+I10+I17+I11*0.5-I12-I13</f>
+        <v/>
+      </c>
+      <c r="J16" s="17">
+        <f>J7+J10+J17+J11*0.5-J12-J13</f>
+        <v/>
+      </c>
+      <c r="K16" s="17">
+        <f>K7+K10+K17+K11*0.4-K12-K13</f>
+        <v/>
+      </c>
+      <c r="L16" s="17">
+        <f>L7+L10+L17+L11*0.4-L12-L13</f>
+        <v/>
+      </c>
+      <c r="M16" s="17">
+        <f>M7+M10+M17+M11*0.4-M12-M13</f>
+        <v/>
+      </c>
+      <c r="N16" s="17">
+        <f>N7+N10+N17+N11*0.4-N12-N13</f>
+        <v/>
+      </c>
+      <c r="O16" s="17">
+        <f>O7+O10+O17+O11*0.2-O12-O13</f>
+        <v/>
+      </c>
+      <c r="P16" s="17">
+        <f>P7+P10+P17+P11*0.2-P12-P13</f>
+        <v/>
+      </c>
+      <c r="Q16" s="17">
+        <f>Q7+Q10+Q17+Q11*0.2-Q12-Q13</f>
+        <v/>
+      </c>
+      <c r="R16" s="17">
+        <f>R7+R10+R17+R11*0.2-R12-R13</f>
+        <v/>
+      </c>
+      <c r="S16" s="17">
+        <f>S7+S10+S17+S11*0.2-S12-S13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Tiền gửi của TCTD khác</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>45606.142</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>60349.404</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>57307.332</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>68284.02899999999</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>61293.738</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>47939.774</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>49594.4</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>57582.142</v>
+      </c>
+      <c r="J17" s="17" t="n">
+        <v>50619.678</v>
+      </c>
+      <c r="K17" s="17" t="n">
+        <v>76496.75599999999</v>
+      </c>
+      <c r="L17" s="17" t="n">
+        <v>60471.427</v>
+      </c>
+      <c r="M17" s="17" t="n">
+        <v>70584.329</v>
+      </c>
+      <c r="N17" s="17" t="n">
+        <v>72210.834</v>
+      </c>
+      <c r="O17" s="17" t="n">
+        <v>81331.394</v>
+      </c>
+      <c r="P17" s="17" t="n">
+        <v>91640.53599999999</v>
+      </c>
+      <c r="Q17" s="17" t="n">
+        <v>93471.217</v>
+      </c>
+      <c r="R17" s="17" t="n">
+        <v>83014.31299999999</v>
+      </c>
+      <c r="S17" s="17" t="n">
+        <v>86820.944</v>
       </c>
     </row>
   </sheetData>
@@ -18347,7 +18569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18703,6 +18925,118 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Tổng tín dụng (tỷ)</t>
+        </is>
+      </c>
+      <c r="B11" s="17">
+        <f>B3+B4</f>
+        <v/>
+      </c>
+      <c r="C11" s="17">
+        <f>C3+C4</f>
+        <v/>
+      </c>
+      <c r="D11" s="17">
+        <f>D3+D4</f>
+        <v/>
+      </c>
+      <c r="E11" s="17">
+        <f>E3+E4</f>
+        <v/>
+      </c>
+      <c r="F11" s="17">
+        <f>F3+F4</f>
+        <v/>
+      </c>
+      <c r="G11" s="17">
+        <f>G3+G4</f>
+        <v/>
+      </c>
+      <c r="H11" s="17">
+        <f>H3+H4</f>
+        <v/>
+      </c>
+      <c r="I11" s="17">
+        <f>I3+I4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Tổng huy động (tỷ)</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
+        <f>B5+B6+B13+B7*0.0-B8-B9</f>
+        <v/>
+      </c>
+      <c r="C12" s="17">
+        <f>C5+C6+C13+C7*0.0-C8-C9</f>
+        <v/>
+      </c>
+      <c r="D12" s="17">
+        <f>D5+D6+D13+D7*0.5-D8-D9</f>
+        <v/>
+      </c>
+      <c r="E12" s="17">
+        <f>E5+E6+E13+E7*0.4-E8-E9</f>
+        <v/>
+      </c>
+      <c r="F12" s="17">
+        <f>F5+F6+F13+F7*0.2-F8-F9</f>
+        <v/>
+      </c>
+      <c r="G12" s="17">
+        <f>G5+G6+G13+G7*0.2-G8-G9</f>
+        <v/>
+      </c>
+      <c r="H12" s="17">
+        <f>H5+H6+H13+H7*0.2-H8-H9</f>
+        <v/>
+      </c>
+      <c r="I12" s="17">
+        <f>I5+I6+I13+I7*0.2-I8-I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Tiền gửi của TCTD khác</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>45606.142</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>61293.738</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>50619.678</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>72210.834</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>83014.31299999999</v>
+      </c>
+      <c r="G13" s="17">
+        <f>F13*(1+'02_Assumptions'!G5)</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>G13*(1+'02_Assumptions'!H5)</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>H13*(1+'02_Assumptions'!I5)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
